--- a/state_art.xlsx
+++ b/state_art.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\archlinux\home\fer\master\PRANK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8276D25B-5E67-4FCA-80CB-E41DE7CD2BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A591053-0469-424C-8938-0A70296C787E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{09A9E53A-B91E-4B74-8B30-AD04FEA3560E}"/>
   </bookViews>
